--- a/registration_forms/020_higher_ed_digital_strategy_network_registration--registration_forms.xlsx
+++ b/registration_forms/020_higher_ed_digital_strategy_network_registration--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -711,8 +711,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="43" customWidth="1" min="2" max="2"/>
-    <col width="43" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,12 +740,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'arizona_state_university'}</t>
+          <t>arizona_state_university</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Arizona State University'}</t>
+          <t>Arizona State University</t>
         </is>
       </c>
     </row>
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'university_of_michigan'}</t>
+          <t>university_of_michigan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'University of Michigan'}</t>
+          <t>University of Michigan</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'university_of_texas'}</t>
+          <t>university_of_texas</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'University of Texas'}</t>
+          <t>University of Texas</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'it_manager'}</t>
+          <t>it_manager</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'IT Manager'}</t>
+          <t>IT Manager</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'digital_strategist'}</t>
+          <t>digital_strategist</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Digital Strategist'}</t>
+          <t>Digital Strategist</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'digital_marketing_specialist'}</t>
+          <t>digital_marketing_specialist</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Digital Marketing Specialist'}</t>
+          <t>Digital Marketing Specialist</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -859,12 +859,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'digital_content_creation'}</t>
+          <t>digital_content_creation</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Digital Content Creation'}</t>
+          <t>Digital Content Creation</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'digital_marketing'}</t>
+          <t>digital_marketing</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Digital Marketing'}</t>
+          <t>Digital Marketing</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
